--- a/ig/ch-term/CodeSystem-ch-vacd-swissmedic-cs.xlsx
+++ b/ig/ch-term/CodeSystem-ch-vacd-swissmedic-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -129,7 +129,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>130</t>
+    <t>133</t>
   </si>
   <si>
     <t>Level</t>
@@ -153,7 +153,7 @@
     <t>FSME-Immun 0.25 ml Junior</t>
   </si>
   <si>
-    <t>FSME-Immun 0.25 ml Junior, Suspension zur intramuskulären Injektion	Pfizer AG</t>
+    <t>FSME-Immun 0.25 ml Junior, Suspension zur intramuskulären Injektion, Pfizer AG</t>
   </si>
   <si>
     <t>450</t>
@@ -162,7 +162,7 @@
     <t>FSME-Immun CC</t>
   </si>
   <si>
-    <t>FSME-Immun CC, Suspension zur intramuskulären Injektion	Pfizer AG</t>
+    <t>FSME-Immun CC, Suspension zur intramuskulären Injektion, Pfizer AG</t>
   </si>
   <si>
     <t>656</t>
@@ -171,7 +171,7 @@
     <t>NeisVac-C</t>
   </si>
   <si>
-    <t>NeisVac-C, Injektionssuspension	Pfizer AG</t>
+    <t>NeisVac-C, Injektionssuspension, Pfizer AG</t>
   </si>
   <si>
     <t>627</t>
@@ -180,7 +180,7 @@
     <t>Encepur N</t>
   </si>
   <si>
-    <t>Encepur N, Injektionssuspension Bavarian Nordic Switzerland AG</t>
+    <t>Encepur N, Injektionssuspension, Bavarian Nordic Switzerland AG</t>
   </si>
   <si>
     <t>628</t>
@@ -189,7 +189,7 @@
     <t>Encepur N Kinder / Enfants</t>
   </si>
   <si>
-    <t>Encepur N Kinder, Injektionssuspension	Bavarian Nordic Switzerland AG</t>
+    <t>Encepur N Kinder, Injektionssuspension, Bavarian Nordic Switzerland AG</t>
   </si>
   <si>
     <t>572</t>
@@ -240,6 +240,9 @@
     <t>Rabipur</t>
   </si>
   <si>
+    <t>Rabipur, Pulver und Lösungsmittel zur Herstellung einer Injektionslösung in einer Fertigspritze, Bavarian Nordic Berna GmbH</t>
+  </si>
+  <si>
     <t>702</t>
   </si>
   <si>
@@ -258,6 +261,9 @@
     <t>Vivotif</t>
   </si>
   <si>
+    <t>Vivotif, Kapseln, Bavarian Nordic Berna GmbH</t>
+  </si>
+  <si>
     <t>637</t>
   </si>
   <si>
@@ -282,7 +288,7 @@
     <t>Engerix-B 10</t>
   </si>
   <si>
-    <t>Engerix-B 10, Injektionssuspension	GlaxoSmithKline AG</t>
+    <t>Engerix-B 10, Injektionssuspension, GlaxoSmithKline AG</t>
   </si>
   <si>
     <t>534</t>
@@ -291,7 +297,7 @@
     <t>Engerix-B 20</t>
   </si>
   <si>
-    <t>Engerix-B 20, Injektionssuspension	GlaxoSmithKline AG</t>
+    <t>Engerix-B 20, Injektionssuspension, GlaxoSmithKline AG</t>
   </si>
   <si>
     <t>583</t>
@@ -306,36 +312,54 @@
     <t>Havrix 1440</t>
   </si>
   <si>
+    <t>Havrix 1440, Injektionssuspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>599</t>
   </si>
   <si>
     <t>Havrix 720</t>
   </si>
   <si>
+    <t>Havrix 720, Injektionssuspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>603</t>
   </si>
   <si>
     <t>Hiberix</t>
   </si>
   <si>
+    <t>Hiberix, Pulver und Lösungsmittel zur Herstellung einer Injektionslösung, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>638</t>
   </si>
   <si>
     <t>Infanrix DTPa-IPV</t>
   </si>
   <si>
+    <t>Infanrix DTPa-IPV, Injektionssuspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>619</t>
   </si>
   <si>
     <t>Infanrix DTPa-IPV+Hib</t>
   </si>
   <si>
+    <t>Infanrix DTPa-IPV+Hib, Pulver und Suspension zur Herstellung einer Injektionssuspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>640</t>
   </si>
   <si>
     <t>Infanrix hexa</t>
   </si>
   <si>
+    <t>Infanrix hexa, Pulver und Suspension zur Herstellung einer Injektionssuspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>652</t>
   </si>
   <si>
@@ -354,7 +378,7 @@
     <t>Priorix</t>
   </si>
   <si>
-    <t>Priorix, Pulver und Lösungsmittel zur Herstellung einer Injektionslösung	GlaxoSmithKline AG	B	22.12.1998	22.12.1998	21.12.2023	J07BD52</t>
+    <t>Priorix, Pulver und Lösungsmittel zur Herstellung einer Injektionslösung, GlaxoSmithKline AG</t>
   </si>
   <si>
     <t>592</t>
@@ -363,12 +387,18 @@
     <t>Twinrix 720/20</t>
   </si>
   <si>
+    <t>Twinrix 720/20, Injektionssuspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>585</t>
   </si>
   <si>
     <t>Varilrix</t>
   </si>
   <si>
+    <t>Varilrix, Pulver und Lösungsmittel zur Herstellung einer Injektionslösung, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>528</t>
   </si>
   <si>
@@ -381,7 +411,7 @@
     <t>HBVAXPRO 40</t>
   </si>
   <si>
-    <t>HBVAXPRO 40, Injektionssuspension MSD Merck Sharp &amp; Dohme AG</t>
+    <t>HBVAXPRO 40, Injektionssuspension, MSD Merck Sharp &amp; Dohme AG</t>
   </si>
   <si>
     <t>610</t>
@@ -396,7 +426,7 @@
     <t>HBVAXPRO 10</t>
   </si>
   <si>
-    <t>HBVAXPRO 10, Injektionssuspension MSD Merck Sharp &amp; Dohme AG</t>
+    <t>HBVAXPRO 10, Injektionssuspension, MSD Merck Sharp &amp; Dohme AG</t>
   </si>
   <si>
     <t>268</t>
@@ -423,13 +453,16 @@
     <t>Pentavac</t>
   </si>
   <si>
+    <t>Pentavac, Poudre et suspension pour suspension injectable, Sanofi-Aventis (Suisse) SA</t>
+  </si>
+  <si>
     <t>509</t>
   </si>
   <si>
     <t>Pneumovax-23</t>
   </si>
   <si>
-    <t>Pneumovax-23, Injektionslösung in einer Fertigspritze	MSD Merck Sharp &amp; Dohme AG</t>
+    <t>Pneumovax-23, Injektionslösung in einer Fertigspritze, MSD Merck Sharp &amp; Dohme AG</t>
   </si>
   <si>
     <t>646</t>
@@ -438,30 +471,45 @@
     <t>Revaxis</t>
   </si>
   <si>
+    <t>Revaxis, suspension injectable, Sanofi-Aventis (Suisse) SA</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
     <t>Stamaril</t>
   </si>
   <si>
+    <t>Stamaril, poudre et solvant pour suspension injectable, Sanofi-Aventis (Suisse) SA</t>
+  </si>
+  <si>
     <t>612</t>
   </si>
   <si>
     <t>Tetravac</t>
   </si>
   <si>
+    <t>Tetravac, suspension injectable, Sanofi-Aventis (Suisse) SA</t>
+  </si>
+  <si>
     <t>417</t>
   </si>
   <si>
     <t>Tollwut Impfstoff Mérieux</t>
   </si>
   <si>
+    <t>Tollwut Impfstoff Mérieux, Poudre et solvant pour suspension injectable, Sanofi-Aventis (Suisse) SA</t>
+  </si>
+  <si>
     <t>688</t>
   </si>
   <si>
     <t>Varivax</t>
   </si>
   <si>
+    <t>Varivax, Pulver und Lösungsmittel zur Herstellung einer Injektionssuspension, MSD Merck Sharp &amp; Dohme AG</t>
+  </si>
+  <si>
     <t>485</t>
   </si>
   <si>
@@ -570,13 +618,16 @@
     <t>Rotarix</t>
   </si>
   <si>
+    <t>Rotarix liquid, orale Suspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>703</t>
   </si>
   <si>
     <t>M-M-RVAXPRO</t>
   </si>
   <si>
-    <t>M-M-RVAXPRO, Lyophilisat und Lösungsmittel	MSD Merck Sharp &amp; Dohme AG</t>
+    <t>M-M-RVAXPRO, Pulver und Lösungsmittel zur Herstellung einer Injektionssuspension, MSD Merck Sharp &amp; Dohme AG</t>
   </si>
   <si>
     <t>58506</t>
@@ -609,7 +660,7 @@
     <t>Prevenar 13</t>
   </si>
   <si>
-    <t>Prevenar 13, Injektionssuspension in einer Fertigspritze	Pfizer AG</t>
+    <t>Prevenar 13, Injektionssuspension in einer Fertigspritze, Pfizer AG</t>
   </si>
   <si>
     <t>59147</t>
@@ -618,12 +669,18 @@
     <t>Ixiaro</t>
   </si>
   <si>
+    <t>IXIARO, Injektionssuspension, Future Health Pharma GmbH</t>
+  </si>
+  <si>
     <t>62502</t>
   </si>
   <si>
     <t>Menveo</t>
   </si>
   <si>
+    <t>Menveo, Pulver und Lösung (Durchstechflaschen), GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
@@ -648,6 +705,9 @@
     <t>Fluarix Tetra</t>
   </si>
   <si>
+    <t>Fluarix Tetra 15 µg / 0.5 ml, Injektionssuspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>66037</t>
   </si>
   <si>
@@ -663,10 +723,22 @@
     <t>ProQuad, Pulver und Lösungsmittel zur Herstellung einer Injektionssuspension, MSD Merck Sharp &amp; Dohme AG</t>
   </si>
   <si>
+    <t>65728</t>
+  </si>
+  <si>
+    <t>Gardasil 9 (Durchstechflasche)</t>
+  </si>
+  <si>
+    <t>Gardasil 9, Injektionssuspension in Durchstechflasche, MSD Merck Sharp &amp; Dohme AG</t>
+  </si>
+  <si>
     <t>65387</t>
   </si>
   <si>
-    <t>Gardasil 9</t>
+    <t>Gardasil 9 (Fertigspritze)</t>
+  </si>
+  <si>
+    <t>Gardasil 9, Injektionssuspension in Fertigspritze,	MSD Merck Sharp &amp; Dohme AG</t>
   </si>
   <si>
     <t>66940</t>
@@ -675,22 +747,25 @@
     <t>Vaxelis</t>
   </si>
   <si>
+    <t>Vaxelis 0.5 ml, Injektionssuspension, Future Health Pharma GmbH</t>
+  </si>
+  <si>
     <t>65730</t>
   </si>
   <si>
     <t>Bexsero</t>
   </si>
   <si>
-    <t>Bexsero, Injektionssuspension GlaxoSmithKline AG</t>
+    <t>Bexsero, Injektionssuspension, GlaxoSmithKline AG</t>
   </si>
   <si>
     <t>68087</t>
   </si>
   <si>
-    <t>Influvac Tetra</t>
-  </si>
-  <si>
-    <t>Influvac Tetra 0.5 ml, Injektionssuspension Mylan Pharma GmbH</t>
+    <t>Influvac Tetra 0.5 ml</t>
+  </si>
+  <si>
+    <t>Influvac Tetra 0.5 ml, Injektionssuspension, Mylan Pharma GmbH</t>
   </si>
   <si>
     <t>66427</t>
@@ -699,7 +774,7 @@
     <t>VaxigripTetra</t>
   </si>
   <si>
-    <t>VaxigripTetra, Suspension pour injection dans une seringue pré-remplie	Sanofi-Aventis (Suisse) SA</t>
+    <t>VaxigripTetra, Suspension pour injection dans une seringue pré-remplie, Sanofi-Aventis (Suisse) SA</t>
   </si>
   <si>
     <t>68267</t>
@@ -708,7 +783,7 @@
     <t>Spikevax (COVID-19 Vaccine, Moderna)</t>
   </si>
   <si>
-    <t>Spikevax, Injektionsdispersion	Moderna Switzerland GmbH</t>
+    <t>Spikevax, Injektionsdispersion, Moderna Switzerland GmbH</t>
   </si>
   <si>
     <t>68225</t>
@@ -717,7 +792,7 @@
     <t>Comirnaty (COVID-19 Vaccine, Pfizer)</t>
   </si>
   <si>
-    <t>Comirnaty, Konzentrat zur Herstellung einer Injektionsdispersion	Pfizer AG</t>
+    <t>Comirnaty, Konzentrat zur Herstellung einer Injektionsdispersion, Pfizer AG</t>
   </si>
   <si>
     <t>68235</t>
@@ -726,7 +801,7 @@
     <t>COVID-19 Vaccine Janssen</t>
   </si>
   <si>
-    <t>COVID-19 Vaccine Janssen, Injektionssuspension	Janssen-Cilag AG</t>
+    <t>COVID-19 Vaccine Janssen, Injektionssuspension, Janssen-Cilag AG</t>
   </si>
   <si>
     <t>67482</t>
@@ -735,7 +810,7 @@
     <t>Flucelvax Tetra</t>
   </si>
   <si>
-    <t>Flucelvax Tetra, Injektionssuspension	Medius AG</t>
+    <t>Flucelvax Tetra, Injektionssuspension, Medius AG</t>
   </si>
   <si>
     <t>67704</t>
@@ -744,7 +819,7 @@
     <t>Efluelda 0.7 ml</t>
   </si>
   <si>
-    <t>Efluelda 0.7 ml, suspension injectable en seringue préremplie	Sanofi-Aventis (Suisse) SA</t>
+    <t>Efluelda 0.7 ml, suspension injectable en seringue préremplie, Sanofi-Aventis (Suisse) SA</t>
   </si>
   <si>
     <t>67987</t>
@@ -753,7 +828,7 @@
     <t>Shingrix</t>
   </si>
   <si>
-    <t>Shingrix, Pulver und Suspension zur Herstellung einer Injektionssuspension	GlaxoSmithKline AG</t>
+    <t>Shingrix, Pulver und Suspension zur Herstellung einer Injektionssuspension, GlaxoSmithKline AG</t>
   </si>
   <si>
     <t>68003</t>
@@ -762,7 +837,7 @@
     <t>Supemtek 0.5 ml</t>
   </si>
   <si>
-    <t>Supemtek 0.5 ml, solution injectable dans une seringue pré-remplie	Sanofi-Aventis (Suisse) SA</t>
+    <t>Supemtek 0.5 ml, solution injectable dans une seringue pré-remplie, Sanofi-Aventis (Suisse) SA</t>
   </si>
   <si>
     <t>66161</t>
@@ -771,7 +846,7 @@
     <t>Foclivia (Durchstechflasche)</t>
   </si>
   <si>
-    <t>Foclivia, Injektionssuspension in einer Durchstechflasche	Emergent BioSolutions Berna GmbH</t>
+    <t>Foclivia, Injektionssuspension in einer Durchstechflasche, Emergent BioSolutions Berna GmbH</t>
   </si>
   <si>
     <t>66156</t>
@@ -780,22 +855,22 @@
     <t>Foclivia (Fertigspritze)</t>
   </si>
   <si>
-    <t>Foclivia, Injektionssuspension in einer Fertigspritze	Emergent BioSolutions Berna GmbH</t>
+    <t>Foclivia, Injektionssuspension in einer Fertigspritze, Emergent BioSolutions Berna GmbH</t>
   </si>
   <si>
     <t>68473</t>
   </si>
   <si>
-    <t>Nuvaxovid 0.5 ml, Injektionsdispersion</t>
-  </si>
-  <si>
-    <t>Nuvaxovid 0.5 ml, Injektionsdispersion,	Future Health Pharma GmbH</t>
+    <t>Nuvaxovid 0.5 ml</t>
+  </si>
+  <si>
+    <t>Nuvaxovid 0.5 ml, Injektionsdispersion, Future Health Pharma GmbH</t>
   </si>
   <si>
     <t>68358</t>
   </si>
   <si>
-    <t>Ervebo, Injektionslösung</t>
+    <t>Ervebo</t>
   </si>
   <si>
     <t>Ervebo, Injektionslösung, MSD Merck Sharp &amp; Dohme AG</t>
@@ -876,7 +951,7 @@
     <t>69123</t>
   </si>
   <si>
-    <t>Spikevax Bivalent Original / Omicron 10 mg/ml, Fertigspritze</t>
+    <t>Spikevax Bivalent Original / Omicron 10 mg/ml</t>
   </si>
   <si>
     <t>Spikevax Bivalent Original / Omicron 10 mg/ml, Fertigspritze, Moderna Switzerland GmbH</t>
@@ -885,7 +960,7 @@
     <t>69010</t>
   </si>
   <si>
-    <t>Spikevax, Fertigspritze</t>
+    <t>Spikevax</t>
   </si>
   <si>
     <t>Spikevax, Fertigspritze,	Moderna Switzerland GmbH</t>
@@ -912,7 +987,7 @@
     <t>69189</t>
   </si>
   <si>
-    <t>Spikevax Bivalent Original / Omicron BA.4-5, dispersion for injection</t>
+    <t>Spikevax Bivalent Original / Omicron BA.4-5</t>
   </si>
   <si>
     <t>Spikevax Bivalent Original / Omicron BA.4-5, dispersion for injection,	Moderna Switzerland GmbH</t>
@@ -921,16 +996,13 @@
     <t>69211</t>
   </si>
   <si>
-    <t>Spikevax Bivalent Original / Omicron BA.4-5, Fertigspritze</t>
-  </si>
-  <si>
     <t>Spikevax Bivalent Original / Omicron BA.4-5, Fertigspritze,	Moderna Switzerland GmbH</t>
   </si>
   <si>
     <t>68752</t>
   </si>
   <si>
-    <t>Vaxneuvance, Injektionssuspension</t>
+    <t>Vaxneuvance</t>
   </si>
   <si>
     <t>Vaxneuvance, Injektionssuspension,	MSD Merck Sharp &amp; Dohme AG</t>
@@ -939,7 +1011,7 @@
     <t>69465</t>
   </si>
   <si>
-    <t>Spikevax XBB.1.5 0.10 mg/ml, Dispersion zur Injektion</t>
+    <t>Spikevax XBB.1.5 0.10 mg/ml</t>
   </si>
   <si>
     <t>Spikevax XBB.1.5 0.10 mg/ml, Dispersion zur Injektion	Moderna Switzerland GmbH</t>
@@ -951,7 +1023,7 @@
     <t>69488</t>
   </si>
   <si>
-    <t>Comirnaty Omicron XBB.1.5 (30 Mikrogramm)/Dosis, Injektionsdispersion</t>
+    <t>Comirnaty Omicron XBB.1.5 (30 Mikrogramm)/Dosis</t>
   </si>
   <si>
     <t>Comirnaty Omicron XBB.1.5 (30 Mikrogramm)/Dosis, Injektionsdispersion	Pfizer AG</t>
@@ -960,124 +1032,169 @@
     <t>69310</t>
   </si>
   <si>
-    <t>AREXVY, Pulver und Suspension zur Herstellung einer Injektionssuspension	GlaxoSmithKline AG</t>
-  </si>
-  <si>
     <t>AREXVY</t>
   </si>
   <si>
+    <t>AREXVY, Pulver und Suspension zur Herstellung einer Injektionssuspension, GlaxoSmithKline AG</t>
+  </si>
+  <si>
     <t>69173</t>
   </si>
   <si>
-    <t>Jynneos, Injektionssuspension	Bavarian Nordic Switzerland AG</t>
-  </si>
-  <si>
     <t>Jynneos</t>
   </si>
   <si>
     <t>69222</t>
   </si>
   <si>
-    <t>Prevenar 20, Injektionssuspension in einer Fertigspritze	Pfizer AG</t>
-  </si>
-  <si>
     <t>Prevenar 20</t>
   </si>
   <si>
+    <t>Prevenar 20, Injektionssuspension in einer Fertigspritze, Pfizer AG</t>
+  </si>
+  <si>
     <t>69815</t>
   </si>
   <si>
-    <t>Comirnaty Omicron XBB.1.5, 0.042 mg, Injektionsdispersion in einer Fertigspritze	Pfizer AG</t>
-  </si>
-  <si>
     <t>Comirnaty Omicron XBB.1.5, 0.042 mg</t>
   </si>
   <si>
     <t>69403</t>
   </si>
   <si>
-    <t>Qdenga 0.5 ml, Pulver und Lösungsmittel für eine Injektionslösung in einer vorgefüllten Spritze	Takeda Pharma AG</t>
-  </si>
-  <si>
-    <t>Qdenga 0.5 ml, Pulver und Lösungsmittel für eine Injektionslösung</t>
+    <t>Qdenga 0.5 ml</t>
+  </si>
+  <si>
+    <t>Qdenga 0.5 ml, Pulver und Lösungsmittel für eine Injektionslösung, Takeda Pharma AG</t>
   </si>
   <si>
     <t>69913</t>
   </si>
   <si>
+    <t>Comirnaty JN.1 0.042 mg</t>
+  </si>
+  <si>
     <t>Comirnaty JN.1 0.042 mg, Injektionsdispersion in einer Fertigspritze, Pfizer AG</t>
   </si>
   <si>
     <t>69912-01</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 30 μg, Injektionsdispersion, Pfizer AG</t>
+    <t>Comirnaty JN.1 30 µg</t>
+  </si>
+  <si>
+    <t>Comirnaty JN.1 30 µg, Injektionsdispersion, Pfizer AG</t>
   </si>
   <si>
     <t>69912-02</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 10 μg, Injektionsdispersion, Pfizer AG</t>
+    <t>Comirnaty JN.1 10 µg</t>
+  </si>
+  <si>
+    <t>Comirnaty JN.1 10 µg, Injektionsdispersion, Pfizer AG</t>
   </si>
   <si>
     <t>69691</t>
   </si>
   <si>
-    <t>Abrysvo, Pulver und Lösungsmittel zur Herstellung einer Injektionslösung, Pfizer AG</t>
+    <t>Abrysvo</t>
   </si>
   <si>
     <t>69788</t>
   </si>
   <si>
+    <t>Spikevax JN.1 (mRNA-1273.167), 0.10mg/ml</t>
+  </si>
+  <si>
     <t>Spikevax JN.1 (mRNA-1273.167), 0.10mg/ml, Dispersion zur Injektion, Moderna Switzerland GmbH</t>
   </si>
   <si>
     <t>69863-01</t>
   </si>
   <si>
-    <t>Efluelda TIV 0.5 mL, suspension injectable en seringue pré-remplie	Sanofi-Aventis (Suisse) SA</t>
+    <t>Efluelda TIV 0.5 mL</t>
+  </si>
+  <si>
+    <t>Efluelda TIV 0.5 mL, suspension injectable en seringue pré-remplie, Sanofi-Aventis (Suisse) SA</t>
   </si>
   <si>
     <t>69995-01</t>
   </si>
   <si>
-    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml, Injektionsdispersion	Moderna Switzerland GmbH</t>
+    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml</t>
+  </si>
+  <si>
+    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml, Injektionsdispersion, Moderna Switzerland GmbH</t>
   </si>
   <si>
     <t>70205</t>
   </si>
   <si>
-    <t>Spikevax LP.8.1 Moderna Switzerland GmbH</t>
+    <t>Spikevax LP.8.1</t>
+  </si>
+  <si>
+    <t>Spikevax LP.8.1, Moderna Switzerland GmbH</t>
   </si>
   <si>
     <t>70400</t>
   </si>
   <si>
-    <t>Comirnaty LP.8.1 10 μg, Injektionsdispersion Pfizer AG</t>
+    <t>Comirnaty LP.8.1 10 μg</t>
+  </si>
+  <si>
+    <t>Comirnaty LP.8.1 10 μg, Injektionsdispersion, Pfizer AG</t>
   </si>
   <si>
     <t>70403</t>
   </si>
   <si>
-    <t>Comirnaty LP.8.1 30 Mikrogramm, Injektionsdispersion in einer Fertigspritze Pfizer AG'</t>
+    <t>Comirnaty LP.8.1 30 Mikrogramm</t>
+  </si>
+  <si>
+    <t>Comirnaty LP.8.1 30 Mikrogramm, Injektionsdispersion in einer Fertigspritze, Pfizer AG</t>
   </si>
   <si>
     <t>69781</t>
   </si>
   <si>
-    <t>Capvaxive, Injektionslösung in Fertigspritze MSD Merck Sharp &amp; Dohme AG</t>
+    <t>Capvaxive</t>
+  </si>
+  <si>
+    <t>Capvaxive, Injektionslösung in Fertigspritze, MSD Merck Sharp &amp; Dohme AG</t>
   </si>
   <si>
     <t>70042</t>
   </si>
   <si>
-    <t>Fluarix, Injektionssuspension GlaxoSmithKline AG</t>
+    <t>Fluarix, Injektionssuspension, GlaxoSmithKline AG</t>
   </si>
   <si>
     <t>69992</t>
   </si>
   <si>
-    <t>Influvac 0.5 ml, Injektionssuspension in einer Fertigspritze Viatris Pharma GmbH</t>
+    <t>Influvac 0.5 ml</t>
+  </si>
+  <si>
+    <t>Influvac 0.5 ml, Injektionssuspension in einer Fertigspritze, Viatris Pharma GmbH</t>
+  </si>
+  <si>
+    <t>70144</t>
+  </si>
+  <si>
+    <t>Flucelvax</t>
+  </si>
+  <si>
+    <t>Flucelvax, Injektionssuspension in einer Fertigspritze, Vifor (International) Inc.</t>
+  </si>
+  <si>
+    <t>70490</t>
+  </si>
+  <si>
+    <t>Vimkunya</t>
+  </si>
+  <si>
+    <t>Vimkunya, Injektionssuspension in einer Fertigspritze, Bavarian Nordic Berna GmbH</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1578,17 +1695,19 @@
       <c r="C14" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>75</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -1597,10 +1716,10 @@
         <v>43</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -1609,22 +1728,24 @@
         <v>43</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2"/>
     </row>
@@ -1633,10 +1754,10 @@
         <v>43</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D19" s="2"/>
     </row>
@@ -1645,10 +1766,10 @@
         <v>43</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D20" s="2"/>
     </row>
@@ -1657,13 +1778,13 @@
         <v>43</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22">
@@ -1671,13 +1792,13 @@
         <v>43</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23">
@@ -1685,10 +1806,10 @@
         <v>43</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2"/>
     </row>
@@ -1697,82 +1818,94 @@
         <v>43</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="D24" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>99</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="D25" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>102</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="D26" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>105</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="D27" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>108</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="D28" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>111</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>114</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D30" s="2"/>
     </row>
@@ -1781,10 +1914,10 @@
         <v>43</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D31" s="2"/>
     </row>
@@ -1793,13 +1926,13 @@
         <v>43</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33">
@@ -1807,34 +1940,38 @@
         <v>43</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="D33" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>124</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>127</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D35" s="2"/>
     </row>
@@ -1843,13 +1980,13 @@
         <v>43</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37">
@@ -1857,10 +1994,10 @@
         <v>43</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D37" s="2"/>
     </row>
@@ -1869,13 +2006,13 @@
         <v>43</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39">
@@ -1883,10 +2020,10 @@
         <v>43</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D39" s="2"/>
     </row>
@@ -1895,10 +2032,10 @@
         <v>43</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="D40" s="2"/>
     </row>
@@ -1907,10 +2044,10 @@
         <v>43</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D41" s="2"/>
     </row>
@@ -1919,25 +2056,27 @@
         <v>43</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="D42" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>146</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44">
@@ -1945,70 +2084,80 @@
         <v>43</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="D44" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>152</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="D45" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>155</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="D46" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>158</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D47" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>161</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="D48" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>164</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -2017,10 +2166,10 @@
         <v>43</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -2029,10 +2178,10 @@
         <v>43</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -2041,10 +2190,10 @@
         <v>43</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -2053,10 +2202,10 @@
         <v>43</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="D53" s="2"/>
     </row>
@@ -2065,10 +2214,10 @@
         <v>43</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -2077,13 +2226,13 @@
         <v>43</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56">
@@ -2091,13 +2240,13 @@
         <v>43</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57">
@@ -2105,10 +2254,10 @@
         <v>43</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -2117,10 +2266,10 @@
         <v>43</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="D58" s="2"/>
     </row>
@@ -2129,10 +2278,10 @@
         <v>43</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="D59" s="2"/>
     </row>
@@ -2141,10 +2290,10 @@
         <v>43</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D60" s="2"/>
     </row>
@@ -2153,10 +2302,10 @@
         <v>43</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D61" s="2"/>
     </row>
@@ -2165,22 +2314,24 @@
         <v>43</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="D62" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>121</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -2189,10 +2340,10 @@
         <v>43</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -2201,25 +2352,27 @@
         <v>43</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="D65" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>201</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>187</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67">
@@ -2227,10 +2380,10 @@
         <v>43</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -2239,10 +2392,10 @@
         <v>43</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -2251,10 +2404,10 @@
         <v>43</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="D69" s="2"/>
     </row>
@@ -2263,10 +2416,10 @@
         <v>43</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -2275,13 +2428,13 @@
         <v>43</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72">
@@ -2289,34 +2442,38 @@
         <v>43</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="D72" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="D72" t="s" s="2">
+        <v>218</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="D73" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="D73" t="s" s="2">
+        <v>221</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="D74" s="2"/>
     </row>
@@ -2325,10 +2482,10 @@
         <v>43</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="D75" s="2"/>
     </row>
@@ -2337,10 +2494,10 @@
         <v>43</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D76" s="2"/>
     </row>
@@ -2349,22 +2506,24 @@
         <v>43</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="D77" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>230</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="D78" s="2"/>
     </row>
@@ -2373,13 +2532,13 @@
         <v>43</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>215</v>
+        <v>235</v>
       </c>
     </row>
     <row r="80">
@@ -2387,37 +2546,41 @@
         <v>43</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="D80" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="D80" t="s" s="2">
+        <v>238</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="D81" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>241</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83">
@@ -2425,13 +2588,13 @@
         <v>43</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>225</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84">
@@ -2439,13 +2602,13 @@
         <v>43</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>228</v>
+        <v>250</v>
       </c>
     </row>
     <row r="85">
@@ -2453,13 +2616,13 @@
         <v>43</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>231</v>
+        <v>253</v>
       </c>
     </row>
     <row r="86">
@@ -2467,13 +2630,13 @@
         <v>43</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87">
@@ -2481,13 +2644,13 @@
         <v>43</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>237</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88">
@@ -2495,13 +2658,13 @@
         <v>43</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>240</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89">
@@ -2509,13 +2672,13 @@
         <v>43</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>243</v>
+        <v>265</v>
       </c>
     </row>
     <row r="90">
@@ -2523,13 +2686,13 @@
         <v>43</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="91">
@@ -2537,13 +2700,13 @@
         <v>43</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>249</v>
+        <v>271</v>
       </c>
     </row>
     <row r="92">
@@ -2551,13 +2714,13 @@
         <v>43</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>252</v>
+        <v>274</v>
       </c>
     </row>
     <row r="93">
@@ -2565,13 +2728,13 @@
         <v>43</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>255</v>
+        <v>277</v>
       </c>
     </row>
     <row r="94">
@@ -2579,13 +2742,13 @@
         <v>43</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>258</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95">
@@ -2593,13 +2756,13 @@
         <v>43</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>261</v>
+        <v>283</v>
       </c>
     </row>
     <row r="96">
@@ -2607,13 +2770,13 @@
         <v>43</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>264</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97">
@@ -2621,13 +2784,13 @@
         <v>43</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>267</v>
+        <v>289</v>
       </c>
     </row>
     <row r="98">
@@ -2635,13 +2798,13 @@
         <v>43</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>270</v>
+        <v>292</v>
       </c>
     </row>
     <row r="99">
@@ -2649,13 +2812,13 @@
         <v>43</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>273</v>
+        <v>295</v>
       </c>
     </row>
     <row r="100">
@@ -2663,13 +2826,13 @@
         <v>43</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>276</v>
+        <v>298</v>
       </c>
     </row>
     <row r="101">
@@ -2677,13 +2840,13 @@
         <v>43</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
     </row>
     <row r="102">
@@ -2691,13 +2854,13 @@
         <v>43</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>282</v>
+        <v>304</v>
       </c>
     </row>
     <row r="103">
@@ -2705,13 +2868,13 @@
         <v>43</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>285</v>
+        <v>307</v>
       </c>
     </row>
     <row r="104">
@@ -2719,13 +2882,13 @@
         <v>43</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>288</v>
+        <v>310</v>
       </c>
     </row>
     <row r="105">
@@ -2733,13 +2896,13 @@
         <v>43</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>291</v>
+        <v>313</v>
       </c>
     </row>
     <row r="106">
@@ -2747,13 +2910,13 @@
         <v>43</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>294</v>
+        <v>316</v>
       </c>
     </row>
     <row r="107">
@@ -2761,13 +2924,13 @@
         <v>43</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>297</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108">
@@ -2775,13 +2938,13 @@
         <v>43</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>300</v>
+        <v>322</v>
       </c>
     </row>
     <row r="109">
@@ -2789,13 +2952,13 @@
         <v>43</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>303</v>
+        <v>325</v>
       </c>
     </row>
     <row r="110">
@@ -2803,13 +2966,13 @@
         <v>43</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>306</v>
+        <v>327</v>
       </c>
     </row>
     <row r="111">
@@ -2817,13 +2980,13 @@
         <v>43</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>309</v>
+        <v>330</v>
       </c>
     </row>
     <row r="112">
@@ -2831,13 +2994,13 @@
         <v>43</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>309</v>
+        <v>333</v>
       </c>
     </row>
     <row r="113">
@@ -2845,13 +3008,13 @@
         <v>43</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="114">
@@ -2859,13 +3022,13 @@
         <v>43</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>316</v>
+        <v>337</v>
       </c>
     </row>
     <row r="115">
@@ -2873,13 +3036,13 @@
         <v>43</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>319</v>
+        <v>340</v>
       </c>
     </row>
     <row r="116">
@@ -2887,13 +3050,13 @@
         <v>43</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>322</v>
+        <v>342</v>
       </c>
     </row>
     <row r="117">
@@ -2901,13 +3064,13 @@
         <v>43</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>325</v>
+        <v>345</v>
       </c>
     </row>
     <row r="118">
@@ -2915,13 +3078,13 @@
         <v>43</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>328</v>
+        <v>347</v>
       </c>
     </row>
     <row r="119">
@@ -2929,13 +3092,13 @@
         <v>43</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row r="120">
@@ -2943,13 +3106,13 @@
         <v>43</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>332</v>
+        <v>353</v>
       </c>
     </row>
     <row r="121">
@@ -2957,13 +3120,13 @@
         <v>43</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>334</v>
+        <v>356</v>
       </c>
     </row>
     <row r="122">
@@ -2971,13 +3134,13 @@
         <v>43</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>336</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123">
@@ -2985,13 +3148,13 @@
         <v>43</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>338</v>
+        <v>361</v>
       </c>
     </row>
     <row r="124">
@@ -2999,13 +3162,13 @@
         <v>43</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>340</v>
+        <v>364</v>
       </c>
     </row>
     <row r="125">
@@ -3013,13 +3176,13 @@
         <v>43</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>342</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126">
@@ -3027,72 +3190,126 @@
         <v>43</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="D126" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="D126" t="s" s="2">
+        <v>370</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="D127" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="D127" t="s" s="2">
+        <v>373</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="D128" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="D128" t="s" s="2">
+        <v>376</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="D129" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="D129" t="s" s="2">
+        <v>379</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="D130" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="D130" t="s" s="2">
+        <v>382</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
         <v>43</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="D131" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="D131" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>393</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
